--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="165">
   <si>
     <t>Mat</t>
   </si>
@@ -85,15 +85,9 @@
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
@@ -103,229 +97,229 @@
     <t>ELIZALDE</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CISNEROS</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
@@ -334,54 +328,24 @@
     <t>NAVA</t>
   </si>
   <si>
-    <t>AULIS</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
     <t>GALLARDO</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
     <t>ALEX SAUL</t>
   </si>
   <si>
@@ -394,9 +358,6 @@
     <t>ALBERTO</t>
   </si>
   <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
     <t>SAUL ALEJANDRO</t>
   </si>
   <si>
@@ -406,51 +367,33 @@
     <t>YAIR ANTONIO</t>
   </si>
   <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
     <t>JOSE AUGUSTO</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
     <t>ANUAR ANTONIO</t>
   </si>
   <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
-  </si>
-  <si>
     <t>ERICK ORLANDO</t>
   </si>
   <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
     <t>RAUL ALEJANDRO</t>
   </si>
   <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
     <t>ERICK MANUEL</t>
   </si>
   <si>
@@ -463,12 +406,6 @@
     <t>VIANEY</t>
   </si>
   <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
     <t>ZURISADAI</t>
   </si>
   <si>
@@ -490,112 +427,91 @@
     <t>YESUA ISIDRO</t>
   </si>
   <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
     <t>JESUS ALBERTO</t>
   </si>
   <si>
     <t>GIOVANNI</t>
   </si>
   <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
     <t>ARELY</t>
   </si>
   <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
     <t>VICTOR YAHIR</t>
   </si>
   <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
     <t>GWINETH</t>
   </si>
   <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>OSWALDO ENRIQUE</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>JOSUE GILBERTO</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -996,16 +912,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>39.47</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1019,16 +938,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1042,16 +964,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>19.35</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1065,16 +990,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1088,16 +1016,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>53.13</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1111,16 +1042,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>56.25</v>
+      </c>
+      <c r="H7">
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1110,7 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1199,7 +1133,7 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1222,7 +1156,7 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1245,7 +1179,7 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1268,7 +1202,7 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1291,7 +1225,7 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1350,16 +1284,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>39.47</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1373,16 +1310,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1396,16 +1336,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>19.35</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1419,16 +1362,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>21.05</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1442,16 +1388,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>53.13</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1465,16 +1414,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>56.25</v>
+      </c>
+      <c r="H7">
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1484,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1522,10 +1474,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1539,16 +1491,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920005</v>
+        <v>19330051920004</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1562,16 +1514,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920004</v>
+        <v>19330051920008</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1585,16 +1537,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920006</v>
+        <v>19330051920016</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1608,16 +1560,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920008</v>
+        <v>19330051920015</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1631,16 +1583,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920016</v>
+        <v>19330051920017</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1654,16 +1606,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920015</v>
+        <v>19330051920018</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1677,16 +1629,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920009</v>
+        <v>18330051920168</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1700,16 +1652,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920017</v>
+        <v>19330051920023</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1723,16 +1675,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920018</v>
+        <v>19330051920026</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1746,16 +1698,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920168</v>
+        <v>19330051920027</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1769,16 +1721,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920020</v>
+        <v>19330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1792,22 +1744,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920022</v>
+        <v>19330051920057</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1815,22 +1767,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920021</v>
+        <v>19330051920058</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1838,22 +1790,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920023</v>
+        <v>19330051920068</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1861,22 +1813,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920026</v>
+        <v>19330051920075</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1884,22 +1836,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18330061460390</v>
+        <v>19330051920223</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1907,22 +1859,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920025</v>
+        <v>19330051920225</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1930,22 +1882,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920027</v>
+        <v>19330051920229</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1953,22 +1905,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920029</v>
+        <v>19330051920230</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1976,22 +1928,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920030</v>
+        <v>19330051920232</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1999,22 +1951,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920031</v>
+        <v>19330051920236</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2022,22 +1974,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920035</v>
+        <v>19330051920228</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -2045,22 +1997,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920038</v>
+        <v>19330051420227</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2068,16 +2020,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920223</v>
+        <v>19330051920404</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2091,16 +2043,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920430</v>
+        <v>19330051920239</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2114,16 +2066,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920225</v>
+        <v>19330051920242</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2137,16 +2089,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920229</v>
+        <v>19330051920245</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2160,22 +2112,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920230</v>
+        <v>19330051920353</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2183,22 +2135,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920232</v>
+        <v>19330051920263</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2206,22 +2158,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920234</v>
+        <v>19330051920085</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -2229,22 +2181,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920429</v>
+        <v>19330051920097</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2252,22 +2204,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920236</v>
+        <v>19330051920100</v>
       </c>
       <c r="B34" t="s">
         <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2275,22 +2227,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920228</v>
+        <v>19330051920102</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -2298,22 +2250,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051420227</v>
+        <v>19330051920106</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2321,22 +2273,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920404</v>
+        <v>19330051920109</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2344,22 +2296,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920239</v>
+        <v>19330051920110</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -2367,22 +2319,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920242</v>
+        <v>19330051920001</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2390,22 +2342,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920245</v>
+        <v>19330051920116</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2413,22 +2365,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920307</v>
+        <v>19330051920117</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -2436,22 +2388,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920309</v>
+        <v>19330051920118</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2459,22 +2411,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920316</v>
+        <v>19330051920119</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -2482,22 +2434,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920318</v>
+        <v>19330051920120</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2505,22 +2457,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>19330051920319</v>
+        <v>19330051920122</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2528,62 +2480,62 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>19330051920323</v>
+        <v>19330051920055</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>19330051920441</v>
+        <v>19330051920059</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>19330051920325</v>
+        <v>19330051920307</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2592,21 +2544,21 @@
         <v>13</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>19330051920332</v>
+        <v>19330051920309</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2615,21 +2567,21 @@
         <v>13</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>19330051920331</v>
+        <v>19330051920316</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2638,21 +2590,21 @@
         <v>13</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>19330051920333</v>
+        <v>19330051920325</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2661,7 +2613,7 @@
         <v>13</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2669,13 +2621,13 @@
         <v>19330051920337</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2684,21 +2636,21 @@
         <v>13</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>19330051920341</v>
+        <v>19330051920345</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2707,559 +2659,168 @@
         <v>13</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>19330051920344</v>
+        <v>19330051920246</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>19330051920440</v>
+        <v>19330051920248</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>19330051920345</v>
+        <v>19330051920249</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="D56" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>19330051920346</v>
+        <v>19330051920260</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>19330051920351</v>
+        <v>19330051920402</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D58" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>19330051920085</v>
+        <v>19330051920400</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D59" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>19330051920084</v>
+        <v>19330051920407</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61">
-        <v>19330051920090</v>
-      </c>
-      <c r="B61" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" t="s">
-        <v>176</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62">
-        <v>19330051920089</v>
-      </c>
-      <c r="B62" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" t="s">
-        <v>75</v>
-      </c>
-      <c r="D62" t="s">
-        <v>177</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>11</v>
-      </c>
-      <c r="G62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63">
-        <v>19330051920097</v>
-      </c>
-      <c r="B63" t="s">
-        <v>69</v>
-      </c>
-      <c r="C63" t="s">
-        <v>110</v>
-      </c>
-      <c r="D63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" t="s">
-        <v>11</v>
-      </c>
-      <c r="G63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64">
-        <v>19330051920100</v>
-      </c>
-      <c r="B64" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" t="s">
-        <v>179</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65">
-        <v>19330051920102</v>
-      </c>
-      <c r="B65" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65" t="s">
-        <v>111</v>
-      </c>
-      <c r="D65" t="s">
-        <v>180</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66">
-        <v>19330051920106</v>
-      </c>
-      <c r="B66" t="s">
-        <v>71</v>
-      </c>
-      <c r="C66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" t="s">
-        <v>181</v>
-      </c>
-      <c r="E66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67">
-        <v>19330051920107</v>
-      </c>
-      <c r="B67" t="s">
-        <v>72</v>
-      </c>
-      <c r="C67" t="s">
-        <v>113</v>
-      </c>
-      <c r="D67" t="s">
-        <v>182</v>
-      </c>
-      <c r="E67" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68">
-        <v>19330051920109</v>
-      </c>
-      <c r="B68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" t="s">
-        <v>70</v>
-      </c>
-      <c r="D68" t="s">
-        <v>183</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69">
-        <v>19330051920110</v>
-      </c>
-      <c r="B69" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" t="s">
-        <v>65</v>
-      </c>
-      <c r="D69" t="s">
-        <v>184</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70">
-        <v>19330051920001</v>
-      </c>
-      <c r="B70" t="s">
-        <v>74</v>
-      </c>
-      <c r="C70" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" t="s">
-        <v>185</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71">
-        <v>19330051920116</v>
-      </c>
-      <c r="B71" t="s">
-        <v>75</v>
-      </c>
-      <c r="C71" t="s">
-        <v>115</v>
-      </c>
-      <c r="D71" t="s">
-        <v>186</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72">
-        <v>19330051920117</v>
-      </c>
-      <c r="B72" t="s">
-        <v>76</v>
-      </c>
-      <c r="C72" t="s">
-        <v>58</v>
-      </c>
-      <c r="D72" t="s">
-        <v>187</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73">
-        <v>19330051920118</v>
-      </c>
-      <c r="B73" t="s">
-        <v>77</v>
-      </c>
-      <c r="C73" t="s">
-        <v>47</v>
-      </c>
-      <c r="D73" t="s">
-        <v>188</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74">
-        <v>19330051920119</v>
-      </c>
-      <c r="B74" t="s">
-        <v>78</v>
-      </c>
-      <c r="C74" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" t="s">
-        <v>189</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>11</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75">
-        <v>19330051920120</v>
-      </c>
-      <c r="B75" t="s">
-        <v>79</v>
-      </c>
-      <c r="C75" t="s">
-        <v>116</v>
-      </c>
-      <c r="D75" t="s">
-        <v>190</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76">
-        <v>19330051920121</v>
-      </c>
-      <c r="B76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" t="s">
-        <v>117</v>
-      </c>
-      <c r="D76" t="s">
-        <v>191</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" t="s">
-        <v>11</v>
-      </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77">
-        <v>19330051920122</v>
-      </c>
-      <c r="B77" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" t="s">
-        <v>118</v>
-      </c>
-      <c r="D77" t="s">
-        <v>192</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>11</v>
-      </c>
-      <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="137">
   <si>
     <t>Mat</t>
   </si>
@@ -82,37 +82,94 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>ALCANTARA</t>
@@ -121,31 +178,64 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CISNEROS</t>
-  </si>
-  <si>
-    <t>LLAME</t>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
   </si>
   <si>
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>MELENDEZ</t>
@@ -154,58 +244,154 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>LEYVA</t>
   </si>
   <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
   </si>
   <si>
     <t>ROMARIO ALDAIR</t>
   </si>
   <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
     <t>SAUL ALEJANDRO</t>
   </si>
   <si>
     <t>LOGAN ZURIEL</t>
   </si>
   <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RENZO JHOVANI</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>NADYA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
   </si>
   <si>
     <t>MOISES EFRAIN</t>
@@ -214,22 +400,34 @@
     <t>BRANDON AXEL</t>
   </si>
   <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>AIDA</t>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
   </si>
   <si>
     <t>MONSERRAT</t>
   </si>
   <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
   </si>
 </sst>
 </file>
@@ -630,19 +828,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -656,19 +854,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -682,19 +880,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>70.97</v>
+        <v>83.87</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -708,19 +906,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -734,19 +932,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -760,19 +958,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -825,16 +1023,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>52.63</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -848,16 +1049,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>29.17</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -871,16 +1075,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>51.61</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -894,16 +1101,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>52.63</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -917,16 +1127,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>53.13</v>
+      </c>
+      <c r="H6">
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -940,16 +1153,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>43.75</v>
+      </c>
+      <c r="H7">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -1002,19 +1218,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>78.95</v>
+        <v>52.63</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1028,19 +1244,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>41.67</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1054,19 +1270,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>70.97</v>
+        <v>51.61</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1080,19 +1296,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>63.16</v>
+        <v>52.63</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1106,19 +1322,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>78.13</v>
+        <v>59.38</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1132,19 +1348,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>71.88</v>
+        <v>53.13</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,16 +1402,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920023</v>
+        <v>18330051920168</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1209,16 +1425,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920040</v>
+        <v>19330051920026</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1232,22 +1448,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920057</v>
+        <v>19330051920038</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1255,22 +1471,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920117</v>
+        <v>19330051920037</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1278,22 +1494,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920118</v>
+        <v>19330051920058</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,269 +1517,269 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920017</v>
+        <v>19330051920067</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920018</v>
+        <v>19330051920068</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920059</v>
+        <v>19330051420227</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051420227</v>
+        <v>19330051920400</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920404</v>
+        <v>19330051920409</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920345</v>
+        <v>19330051920094</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920246</v>
+        <v>19330051920101</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920248</v>
+        <v>19330051920105</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920249</v>
+        <v>19330051920001</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920260</v>
+        <v>19330051920118</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920407</v>
+        <v>19330051920119</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920097</v>
+        <v>19330051920120</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1572,27 +1788,27 @@
         <v>11</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920100</v>
+        <v>19330051920003</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1600,24 +1816,668 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920106</v>
+        <v>19330051920004</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920016</v>
+      </c>
+      <c r="B21" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920017</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920018</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920055</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>19330051920223</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>19330051920430</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>19330051920225</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>19330051920230</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>19330051920236</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>19330051920239</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>19330051920242</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>19330051920307</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>19330051920312</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>19330051920316</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>19330051920325</v>
+      </c>
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>19330051920337</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>19330051920246</v>
+      </c>
+      <c r="B37" t="s">
         <v>51</v>
       </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>19330051920248</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>19330051920250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" t="s">
+        <v>127</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>19330051920254</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>19330051920265</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>19330051920402</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>19330051920407</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>19330051920414</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>19330051920085</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
         <v>11</v>
       </c>
-      <c r="G20">
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>19330051920102</v>
+      </c>
+      <c r="B46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>19330051920110</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>19330051920122</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
   <si>
     <t>Mat</t>
   </si>
@@ -88,207 +88,216 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TREJO</t>
   </si>
   <si>
     <t>TAPIA</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>TOCOHUA</t>
   </si>
   <si>
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
@@ -298,133 +307,136 @@
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
     <t>ERICK ORLANDO</t>
   </si>
   <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>NADYA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>YAEL</t>
   </si>
   <si>
     <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>NADYA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANGEL EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
   <si>
     <t>ADOLFO</t>
@@ -1370,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1411,7 +1423,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1431,10 +1443,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1448,16 +1460,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920038</v>
+        <v>19330051920037</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1471,22 +1483,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920037</v>
+        <v>19330051920058</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1494,16 +1506,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920058</v>
+        <v>19330051920068</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1517,22 +1529,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920067</v>
+        <v>19330051920227</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1540,22 +1552,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920068</v>
+        <v>19330051920233</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1566,13 +1578,13 @@
         <v>19330051420227</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1586,22 +1598,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920400</v>
+        <v>19330051920338</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1609,16 +1621,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920409</v>
+        <v>19330051920402</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1632,22 +1644,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920094</v>
+        <v>19330051920400</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1655,16 +1667,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920101</v>
+        <v>19330051920094</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1678,16 +1690,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920105</v>
+        <v>19330051920101</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1701,16 +1713,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920001</v>
+        <v>19330051920105</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1724,16 +1736,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920118</v>
+        <v>19330051920001</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1747,16 +1759,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920119</v>
+        <v>19330051920118</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1770,16 +1782,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920120</v>
+        <v>19330051920119</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1796,13 +1808,13 @@
         <v>19330051920003</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1819,13 +1831,13 @@
         <v>19330051920004</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1842,13 +1854,13 @@
         <v>19330051920016</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1865,13 +1877,13 @@
         <v>19330051920017</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1888,13 +1900,13 @@
         <v>19330051920018</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1908,22 +1920,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920055</v>
+        <v>19330051920038</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1931,22 +1943,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920223</v>
+        <v>19330051920055</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1954,16 +1966,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920430</v>
+        <v>19330051920223</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1977,16 +1989,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920225</v>
+        <v>19330051920430</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2000,16 +2012,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920230</v>
+        <v>19330051920225</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2023,16 +2035,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920236</v>
+        <v>19330051920230</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2046,16 +2058,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920239</v>
+        <v>19330051920236</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2069,16 +2081,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920242</v>
+        <v>19330051920239</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2092,22 +2104,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920307</v>
+        <v>19330051920242</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2115,16 +2127,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920312</v>
+        <v>19330051920307</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2138,16 +2150,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920316</v>
+        <v>19330051920312</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2161,16 +2173,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920325</v>
+        <v>19330051920316</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2184,16 +2196,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920337</v>
+        <v>19330051920325</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2207,22 +2219,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920246</v>
+        <v>19330051920337</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2230,16 +2242,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920248</v>
+        <v>19330051920246</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2253,16 +2265,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920250</v>
+        <v>19330051920248</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2276,16 +2288,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920254</v>
+        <v>19330051920250</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2299,16 +2311,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920265</v>
+        <v>19330051920254</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2322,16 +2334,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920402</v>
+        <v>19330051920265</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2348,13 +2360,13 @@
         <v>19330051920407</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2371,13 +2383,13 @@
         <v>19330051920414</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2394,13 +2406,13 @@
         <v>19330051920085</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2417,13 +2429,13 @@
         <v>19330051920102</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2440,13 +2452,13 @@
         <v>19330051920110</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2460,16 +2472,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>19330051920122</v>
+        <v>19330051920120</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2478,6 +2490,29 @@
         <v>11</v>
       </c>
       <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>19330051920122</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
@@ -1165,16 +1165,16 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>43.75</v>
+        <v>46.88</v>
       </c>
       <c r="H7">
         <v>6.2</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="162">
   <si>
     <t>Mat</t>
   </si>
@@ -82,43 +82,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CHORA</t>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>LADINO</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
   </si>
   <si>
     <t>MONSALVO</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>HERRERA</t>
@@ -133,69 +217,6 @@
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>TAPIA</t>
   </si>
   <si>
@@ -211,21 +232,93 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
     <t>QUINTERO</t>
   </si>
   <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>GARATE</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>ANTEMATE</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>AVELINO</t>
   </si>
   <si>
@@ -235,97 +328,124 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>ABDIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
     <t>YAIR ANTONIO</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
     <t>MAURICIO</t>
   </si>
   <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
   </si>
   <si>
     <t>URIEL</t>
   </si>
   <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
     <t>ALEXANDER</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
+    <t>NADYA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>VICTOR YAHIR</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
   </si>
   <si>
     <t>ALFREDO</t>
@@ -334,15 +454,42 @@
     <t>ANGEL GERARDO</t>
   </si>
   <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
     <t>JOSUE</t>
   </si>
   <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
     <t>AXEL MIGUEL</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>AXEL</t>
   </si>
   <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
     <t>ARIAN ALEXIS</t>
   </si>
   <si>
@@ -350,90 +497,6 @@
   </si>
   <si>
     <t>YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>NADYA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANGEL EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
   <si>
     <t>MARIA ISABEL</t>
@@ -1268,7 +1331,7 @@
         <v>41.67</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1382,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1414,16 +1477,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920168</v>
+        <v>19330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1437,22 +1500,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920026</v>
+        <v>19330051920058</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1460,22 +1523,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920037</v>
+        <v>19330051920068</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1483,22 +1546,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920058</v>
+        <v>19330051920227</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1506,22 +1569,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920068</v>
+        <v>19330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1529,16 +1592,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920227</v>
+        <v>19330051920243</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1552,22 +1615,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920233</v>
+        <v>19330051920338</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1575,22 +1638,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051420227</v>
+        <v>19330051920265</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1598,22 +1661,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920338</v>
+        <v>19330051920098</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1621,200 +1684,200 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920402</v>
+        <v>19330051920003</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920400</v>
+        <v>19330051920004</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920094</v>
+        <v>19330051920016</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920101</v>
+        <v>19330051920017</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920105</v>
+        <v>19330051920018</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920001</v>
+        <v>18330051920168</v>
       </c>
       <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920118</v>
+        <v>19330051920026</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920119</v>
+        <v>19330051920024</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920003</v>
+        <v>19330051920038</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1828,16 +1891,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920004</v>
+        <v>19330051920037</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1851,16 +1914,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920016</v>
+        <v>19330051920039</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1874,22 +1937,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920017</v>
+        <v>19330051920055</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1897,22 +1960,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920018</v>
+        <v>19330051920223</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1920,22 +1983,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920038</v>
+        <v>19330051920430</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1943,22 +2006,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920055</v>
+        <v>19330051920225</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1966,16 +2029,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920223</v>
+        <v>19330051920230</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1989,16 +2052,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920430</v>
+        <v>19330051920233</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2012,16 +2075,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920225</v>
+        <v>19330051920236</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2035,16 +2098,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920230</v>
+        <v>19330051420227</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2058,16 +2121,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920236</v>
+        <v>19330051920239</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2081,16 +2144,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920239</v>
+        <v>19330051920242</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2104,22 +2167,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920242</v>
+        <v>19330051920307</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2127,16 +2190,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920307</v>
+        <v>19330051920312</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2150,16 +2213,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920312</v>
+        <v>19330051920316</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2173,16 +2236,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920316</v>
+        <v>19330051920325</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2196,16 +2259,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920325</v>
+        <v>19330051920337</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2219,22 +2282,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920337</v>
+        <v>19330051920246</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2242,16 +2305,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920246</v>
+        <v>19330051920248</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2265,16 +2328,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920248</v>
+        <v>19330051920250</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2288,16 +2351,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920250</v>
+        <v>19330051920254</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2311,16 +2374,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920254</v>
+        <v>19330051920258</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2334,16 +2397,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920265</v>
+        <v>19330051920402</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2357,16 +2420,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920407</v>
+        <v>19330051920400</v>
       </c>
       <c r="B43" t="s">
         <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2380,16 +2443,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920414</v>
+        <v>19330051920407</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2403,22 +2466,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>19330051920085</v>
+        <v>19330051920409</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2426,22 +2489,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>19330051920102</v>
+        <v>19330051920414</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2449,16 +2512,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>19330051920110</v>
+        <v>19330051920085</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2472,16 +2535,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>19330051920120</v>
+        <v>19330051920094</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2495,16 +2558,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>19330051920122</v>
+        <v>19330051920095</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2513,6 +2576,259 @@
         <v>11</v>
       </c>
       <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>19330051920099</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>19330051920101</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>19330051920102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>19330051920105</v>
+      </c>
+      <c r="B53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>19330051920110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>19330051920112</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D55" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>19330051920001</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" t="s">
+        <v>157</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>19330051920118</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>19330051920119</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>19330051920120</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" t="s">
+        <v>160</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>19330051920122</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" t="s">
+        <v>161</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="162">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
@@ -202,9 +205,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
@@ -223,6 +223,9 @@
     <t>TOCOHUA</t>
   </si>
   <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
@@ -328,7 +331,7 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>JOHNNY</t>
@@ -347,9 +350,6 @@
   </si>
   <si>
     <t>ABDIEL ANTONIO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>KARLA</t>
@@ -1445,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920034</v>
+        <v>19330051920014</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
         <v>104</v>
@@ -1500,13 +1500,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920058</v>
+        <v>19330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>105</v>
@@ -1515,7 +1515,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920068</v>
+        <v>19330051920058</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920227</v>
+        <v>19330051920068</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920237</v>
+        <v>19330051920227</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1592,7 +1592,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920243</v>
+        <v>19330051920237</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1615,13 +1615,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920338</v>
+        <v>19330051920243</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>110</v>
@@ -1630,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1638,22 +1638,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920265</v>
+        <v>19330051920338</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920098</v>
+        <v>19330051920265</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1684,30 +1684,30 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920003</v>
+        <v>19330051920098</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920004</v>
+        <v>19330051920003</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1716,7 +1716,7 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920016</v>
+        <v>19330051920004</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1739,7 +1739,7 @@
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1753,16 +1753,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920017</v>
+        <v>19330051920016</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
         <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1776,16 +1776,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920018</v>
+        <v>19330051920017</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1799,16 +1799,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920168</v>
+        <v>19330051920018</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1822,16 +1822,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920026</v>
+        <v>18330051920168</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1845,16 +1845,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920024</v>
+        <v>19330051920026</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1868,16 +1868,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920038</v>
+        <v>19330051920024</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1891,16 +1891,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920037</v>
+        <v>19330051920038</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920039</v>
+        <v>19330051920037</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920055</v>
+        <v>19330051920039</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
@@ -1946,13 +1946,13 @@
         <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920223</v>
+        <v>19330051920055</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1969,13 +1969,13 @@
         <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1983,16 +1983,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920430</v>
+        <v>19330051920223</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2006,16 +2006,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920225</v>
+        <v>19330051920430</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2029,16 +2029,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920230</v>
+        <v>19330051920225</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2052,16 +2052,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920233</v>
+        <v>19330051920230</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2075,16 +2075,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920236</v>
+        <v>19330051920233</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2098,16 +2098,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051420227</v>
+        <v>19330051920236</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920239</v>
+        <v>19330051420227</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
@@ -2130,7 +2130,7 @@
         <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2144,16 +2144,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920242</v>
+        <v>19330051920239</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2167,22 +2167,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920307</v>
+        <v>19330051920242</v>
       </c>
       <c r="B32" t="s">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2190,16 +2190,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920312</v>
+        <v>19330051920307</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
         <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2213,16 +2213,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330051920316</v>
+        <v>19330051920312</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2236,16 +2236,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920325</v>
+        <v>19330051920316</v>
       </c>
       <c r="B35" t="s">
         <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920337</v>
+        <v>19330051920325</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
@@ -2268,7 +2268,7 @@
         <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920246</v>
+        <v>19330051920337</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -2291,13 +2291,13 @@
         <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2305,16 +2305,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920248</v>
+        <v>19330051920246</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2328,16 +2328,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920250</v>
+        <v>19330051920248</v>
       </c>
       <c r="B39" t="s">
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2351,16 +2351,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19330051920254</v>
+        <v>19330051920250</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920258</v>
+        <v>19330051920254</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2397,16 +2397,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920402</v>
+        <v>19330051920258</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
         <v>92</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2420,16 +2420,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920400</v>
+        <v>19330051920402</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C43" t="s">
         <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2443,16 +2443,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>19330051920407</v>
+        <v>19330051920400</v>
       </c>
       <c r="B44" t="s">
         <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>19330051920409</v>
+        <v>19330051920407</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2489,16 +2489,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>19330051920414</v>
+        <v>19330051920409</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>19330051920085</v>
+        <v>19330051920414</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
         <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2535,16 +2535,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>19330051920094</v>
+        <v>19330051920085</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
         <v>96</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2558,16 +2558,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>19330051920095</v>
+        <v>19330051920094</v>
       </c>
       <c r="B49" t="s">
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2581,16 +2581,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>19330051920099</v>
+        <v>19330051920095</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2604,16 +2604,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>19330051920101</v>
+        <v>19330051920099</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C51" t="s">
         <v>98</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2627,16 +2627,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>19330051920102</v>
+        <v>19330051920101</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2650,16 +2650,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>19330051920105</v>
+        <v>19330051920102</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
         <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2673,16 +2673,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>19330051920110</v>
+        <v>19330051920105</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2696,16 +2696,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>19330051920112</v>
+        <v>19330051920110</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2719,16 +2719,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>19330051920001</v>
+        <v>19330051920112</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2742,16 +2742,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>19330051920118</v>
+        <v>19330051920001</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2765,16 +2765,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>19330051920119</v>
+        <v>19330051920118</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2788,16 +2788,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>19330051920120</v>
+        <v>19330051920119</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2811,16 +2811,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>19330051920122</v>
+        <v>19330051920120</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2829,6 +2829,29 @@
         <v>11</v>
       </c>
       <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>19330051920122</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61">
         <v>1</v>
       </c>
     </row>
